--- a/Result/profitability/2480.xlsx
+++ b/Result/profitability/2480.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.3</v>
       </c>
       <c r="M2" t="n">
-        <v>1.825</v>
+        <v>1.8975</v>
       </c>
       <c r="N2" t="n">
-        <v>24.7925</v>
+        <v>24.4375</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.34</v>
       </c>
       <c r="M3" t="n">
-        <v>1.65375</v>
+        <v>1.69375</v>
       </c>
       <c r="N3" t="n">
-        <v>25.78</v>
+        <v>25.6525</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.36</v>
       </c>
       <c r="M4" t="n">
-        <v>1.4525</v>
+        <v>1.45875</v>
       </c>
       <c r="N4" t="n">
-        <v>26.435</v>
+        <v>26.0925</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.18</v>
       </c>
       <c r="M5" t="n">
-        <v>1.195</v>
+        <v>1.2425</v>
       </c>
       <c r="N5" t="n">
-        <v>26.50625</v>
+        <v>26.37875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.47</v>
       </c>
       <c r="M6" t="n">
-        <v>1.015</v>
+        <v>1.07875</v>
       </c>
       <c r="N6" t="n">
-        <v>27.3025</v>
+        <v>26.995</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.49</v>
       </c>
       <c r="M7" t="n">
-        <v>0.85375</v>
+        <v>0.8825</v>
       </c>
       <c r="N7" t="n">
-        <v>28.65</v>
+        <v>28.43125</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.54</v>
       </c>
       <c r="M8" t="n">
-        <v>0.66375</v>
+        <v>0.62125</v>
       </c>
       <c r="N8" t="n">
-        <v>29.16375</v>
+        <v>29.0225</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2480</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2462</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1912</v>
+      </c>
+      <c r="E75" t="n">
+        <v>550</v>
+      </c>
+      <c r="F75" t="n">
+        <v>22.33</v>
+      </c>
+      <c r="G75" t="n">
+        <v>291</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>11.81%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>15</v>
+      </c>
+      <c r="J75" t="n">
+        <v>306</v>
+      </c>
+      <c r="K75" t="n">
+        <v>243</v>
+      </c>
+      <c r="L75" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="M75" t="n">
+        <v>2.07375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>23.95</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.3399999999999999</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.1292775665399239</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-1.130000000000003</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.04816709292412624</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.3800000000000001</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.1989528795811519</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-1.020000000000003</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.04368308351177741</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
